--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269488</v>
+        <v>120269482</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632692</v>
+        <v>632679</v>
       </c>
       <c r="R2" t="n">
-        <v>6514924</v>
+        <v>6514919</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269492</v>
+        <v>120269461</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,35 +807,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632685</v>
+        <v>632695</v>
       </c>
       <c r="R3" t="n">
-        <v>6514919</v>
+        <v>6514918</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269465</v>
+        <v>120269488</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,45 +928,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632565</v>
+        <v>632692</v>
       </c>
       <c r="R4" t="n">
-        <v>6515211</v>
+        <v>6514924</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -997,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269461</v>
+        <v>120269495</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,32 +1052,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632695</v>
+        <v>632526</v>
       </c>
       <c r="R5" t="n">
-        <v>6514918</v>
+        <v>6515276</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269495</v>
+        <v>120269465</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,45 +1164,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632526</v>
+        <v>632565</v>
       </c>
       <c r="R6" t="n">
-        <v>6515276</v>
+        <v>6515211</v>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269482</v>
+        <v>120269492</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632679</v>
+        <v>632685</v>
       </c>
       <c r="R7" t="n">
         <v>6514919</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269482</v>
+        <v>120269461</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632679</v>
+        <v>632695</v>
       </c>
       <c r="R2" t="n">
-        <v>6514919</v>
+        <v>6514918</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269461</v>
+        <v>120269482</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,36 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632695</v>
+        <v>632679</v>
       </c>
       <c r="R3" t="n">
-        <v>6514918</v>
+        <v>6514919</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269495</v>
+        <v>120269492</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,28 +1048,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1080,13 +1084,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632526</v>
+        <v>632685</v>
       </c>
       <c r="R5" t="n">
-        <v>6515276</v>
+        <v>6514919</v>
       </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269465</v>
+        <v>120269495</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,48 +1168,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632565</v>
+        <v>632526</v>
       </c>
       <c r="R6" t="n">
-        <v>6515211</v>
+        <v>6515276</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269492</v>
+        <v>120269465</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,46 +1284,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632685</v>
+        <v>632565</v>
       </c>
       <c r="R7" t="n">
-        <v>6514919</v>
+        <v>6515211</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269461</v>
+        <v>120269492</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632695</v>
+        <v>632685</v>
       </c>
       <c r="R2" t="n">
-        <v>6514918</v>
+        <v>6514919</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269482</v>
+        <v>120269495</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,32 +807,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -844,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632679</v>
+        <v>632526</v>
       </c>
       <c r="R3" t="n">
-        <v>6514919</v>
+        <v>6515276</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269488</v>
+        <v>120269465</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,46 +923,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632692</v>
+        <v>632565</v>
       </c>
       <c r="R4" t="n">
-        <v>6514924</v>
+        <v>6515211</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -999,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269492</v>
+        <v>120269488</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1071,7 +1065,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1084,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632685</v>
+        <v>632692</v>
       </c>
       <c r="R5" t="n">
-        <v>6514919</v>
+        <v>6514924</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1119,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269495</v>
+        <v>120269482</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,28 +1162,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1200,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632526</v>
+        <v>632679</v>
       </c>
       <c r="R6" t="n">
-        <v>6515276</v>
+        <v>6514919</v>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269465</v>
+        <v>120269461</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,45 +1282,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632565</v>
+        <v>632695</v>
       </c>
       <c r="R7" t="n">
-        <v>6515211</v>
+        <v>6514918</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269495</v>
+        <v>120269488</v>
       </c>
       <c r="B3" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,28 +807,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -839,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632526</v>
+        <v>632692</v>
       </c>
       <c r="R3" t="n">
-        <v>6515276</v>
+        <v>6514924</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269465</v>
+        <v>120269482</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,48 +927,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632565</v>
+        <v>632679</v>
       </c>
       <c r="R4" t="n">
-        <v>6515211</v>
+        <v>6514919</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269488</v>
+        <v>120269461</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,35 +1047,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1078,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632692</v>
+        <v>632695</v>
       </c>
       <c r="R5" t="n">
-        <v>6514924</v>
+        <v>6514918</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1113,7 +1119,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1129,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269482</v>
+        <v>120269465</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,49 +1168,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632679</v>
+        <v>632565</v>
       </c>
       <c r="R6" t="n">
-        <v>6514919</v>
+        <v>6515211</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1248,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269461</v>
+        <v>120269495</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,32 +1291,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632695</v>
+        <v>632526</v>
       </c>
       <c r="R7" t="n">
-        <v>6514918</v>
+        <v>6515276</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269492</v>
+        <v>120269495</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632685</v>
+        <v>632526</v>
       </c>
       <c r="R2" t="n">
-        <v>6514919</v>
+        <v>6515276</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269488</v>
+        <v>120269492</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -830,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -843,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632692</v>
+        <v>632685</v>
       </c>
       <c r="R3" t="n">
-        <v>6514924</v>
+        <v>6514919</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269482</v>
+        <v>120269461</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>4772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,35 +923,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632679</v>
+        <v>632695</v>
       </c>
       <c r="R4" t="n">
-        <v>6514919</v>
+        <v>6514918</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269461</v>
+        <v>120269482</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,36 +1044,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1084,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632695</v>
+        <v>632679</v>
       </c>
       <c r="R5" t="n">
-        <v>6514918</v>
+        <v>6514919</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269465</v>
+        <v>120269488</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,45 +1164,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632565</v>
+        <v>632692</v>
       </c>
       <c r="R6" t="n">
-        <v>6515211</v>
+        <v>6514924</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1238,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269495</v>
+        <v>120269465</v>
       </c>
       <c r="B7" t="n">
-        <v>100194</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,45 +1284,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632526</v>
+        <v>632565</v>
       </c>
       <c r="R7" t="n">
-        <v>6515276</v>
+        <v>6515211</v>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269495</v>
+        <v>120269492</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632526</v>
+        <v>632685</v>
       </c>
       <c r="R2" t="n">
-        <v>6515276</v>
+        <v>6514919</v>
       </c>
       <c r="S2" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269492</v>
+        <v>120269495</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,32 +807,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632685</v>
+        <v>632526</v>
       </c>
       <c r="R3" t="n">
-        <v>6514919</v>
+        <v>6515276</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269482</v>
+        <v>120269488</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632679</v>
+        <v>632692</v>
       </c>
       <c r="R5" t="n">
-        <v>6514919</v>
+        <v>6514924</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269488</v>
+        <v>120269465</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,46 +1164,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632692</v>
+        <v>632565</v>
       </c>
       <c r="R6" t="n">
-        <v>6514924</v>
+        <v>6515211</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1235,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1271,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269465</v>
+        <v>120269482</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,48 +1283,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632565</v>
+        <v>632679</v>
       </c>
       <c r="R7" t="n">
-        <v>6515211</v>
+        <v>6514919</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269492</v>
+        <v>120269465</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632685</v>
+        <v>632565</v>
       </c>
       <c r="R2" t="n">
-        <v>6514919</v>
+        <v>6515211</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -911,10 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269461</v>
+        <v>120269492</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,36 +922,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632695</v>
+        <v>632685</v>
       </c>
       <c r="R4" t="n">
-        <v>6514918</v>
+        <v>6514919</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269488</v>
+        <v>120269482</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1067,7 +1065,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1080,13 +1078,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632692</v>
+        <v>632679</v>
       </c>
       <c r="R5" t="n">
-        <v>6514924</v>
+        <v>6514919</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269465</v>
+        <v>120269488</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,45 +1162,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632565</v>
+        <v>632692</v>
       </c>
       <c r="R6" t="n">
-        <v>6515211</v>
+        <v>6514924</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1234,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120269482</v>
+        <v>120269461</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1283,35 +1282,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632679</v>
+        <v>632695</v>
       </c>
       <c r="R7" t="n">
-        <v>6514919</v>
+        <v>6514918</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120269461</v>
+        <v>120712563</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632695</v>
+        <v>632565</v>
       </c>
       <c r="R2" t="n">
-        <v>6514918</v>
+        <v>6515211</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +775,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120269495</v>
+        <v>120269461</v>
       </c>
       <c r="B3" t="n">
-        <v>100263</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,27 +805,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632526</v>
+        <v>632695</v>
       </c>
       <c r="R3" t="n">
-        <v>6515276</v>
+        <v>6514918</v>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +883,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +910,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120269492</v>
+        <v>120269485</v>
       </c>
       <c r="B4" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,11 +938,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -960,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632685</v>
+        <v>632691</v>
       </c>
       <c r="R4" t="n">
-        <v>6514919</v>
+        <v>6514948</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mängder längs stigen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120269488</v>
+        <v>120269482</v>
       </c>
       <c r="B5" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1056,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1080,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632692</v>
+        <v>632679</v>
       </c>
       <c r="R5" t="n">
-        <v>6514924</v>
+        <v>6514919</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,15 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120269482</v>
+        <v>120269488</v>
       </c>
       <c r="B6" t="n">
-        <v>97999</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1171,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1200,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632679</v>
+        <v>632692</v>
       </c>
       <c r="R6" t="n">
-        <v>6514919</v>
+        <v>6514924</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,61 +1256,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120712563</v>
+        <v>120269492</v>
       </c>
       <c r="B7" t="n">
-        <v>91991</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömmingsvarpet, Srm</t>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632565</v>
+        <v>632685</v>
       </c>
       <c r="R7" t="n">
-        <v>6515211</v>
+        <v>6514919</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1358,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1353,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1393,6 +1368,117 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120269495</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strömmingsvarpet, Strömmingsvarpet, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>632526</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6515276</v>
+      </c>
+      <c r="S8" t="n">
+        <v>60</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tystberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33265-2024 artfynd.xlsx
+++ b/artfynd/A 33265-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120712563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269461</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269485</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269482</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,8 +1514,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120269495</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>